--- a/ExcelTemplate.xlsx
+++ b/ExcelTemplate.xlsx
@@ -8,14 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://parkersaccountancy.sharepoint.com/sites/ParkersAccountancy/Shared Documents/George/PDF-Converter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE894061-B1CA-4F02-BBC5-E3F190B4CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="8_{DE894061-B1CA-4F02-BBC5-E3F190B4CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C629BEAA-1B7B-4AD6-A51B-CCF5C8EC98B9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CD86054-7E87-4B94-B8DC-63B30BDED129}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3F22E0B9-65B0-45DD-B4C4-92AA6084518F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Helper" sheetId="5" state="hidden" r:id="rId1"/>
+    <sheet name="Custom Rules" sheetId="3" r:id="rId2"/>
+    <sheet name="Transaction Data" sheetId="2" r:id="rId3"/>
+    <sheet name="Summary" sheetId="6" r:id="rId4"/>
+    <sheet name="Pivot Summary" sheetId="4" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,12 +45,151 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+  <si>
+    <t>T/N</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Transaction Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Match Type</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Txn Type Contains</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Global Category</t>
+  </si>
+  <si>
+    <t>ANY</t>
+  </si>
+  <si>
+    <t>Sort the table by Priority (smallest first). First matching rule wins.</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>DEBIT</t>
+  </si>
+  <si>
+    <t>STARTSWITH</t>
+  </si>
+  <si>
+    <t>CREDIT</t>
+  </si>
+  <si>
+    <t>EXACT</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount </t>
+  </si>
+  <si>
+    <t>Expenses</t>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Total:</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -48,6 +197,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -68,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -76,29 +232,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{AD3A82D4-3506-482D-AE4B-1B4C2D0DB15A}"/>
     <cellStyle name="Review" xfId="1" xr:uid="{6CCA6ACB-F3BA-4A8E-992F-9417AD37E0FC}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <border>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </horizontal>
-      </border>
+  <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -229,21 +475,31 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultPivotStyle="PivotStyleLight15 2">
     <tableStyle name="PivotStyleLight15 2" table="0" count="12" xr9:uid="{B38C1715-376E-4820-8142-5B9A7F3A5B04}">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="totalRow" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="9"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="7"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
-      <tableStyleElement type="pageFieldValues" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="26"/>
+      <tableStyleElement type="headerRow" dxfId="25"/>
+      <tableStyleElement type="totalRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
+      <tableStyleElement type="firstSubtotalColumn" dxfId="21"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="20"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="18"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="17"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="16"/>
+      <tableStyleElement type="pageFieldValues" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -260,6 +516,328 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Helper"/>
+      <sheetName val="Custom Rules"/>
+      <sheetName val="Transaction Data"/>
+      <sheetName val="Summary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="G1" t="e">
+            <v>#VALUE!</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="George Farrell" refreshedDate="46086.704445949072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{E30527A9-8550-465B-90F3-1350603B8E86}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="TransactionData"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="T/N" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Transaction Type" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Description" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="44">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Balance" numFmtId="44">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Global" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Custom" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Manual" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Final" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="1">
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86028C4-318E-4098-AF19-D8817826B302}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Income">
+  <location ref="A1:B2" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Amount " fld="4" baseField="9" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight15 2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="9" type="valueGreaterThan" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters>
+            <customFilter operator="greaterThan" val="0"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C87894D-13D6-46EA-81BF-345BEBF15C8B}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expenses">
+  <location ref="D1:E2" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Amount " fld="4" baseField="9" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="14">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight15 2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="9" type="valueLessThan" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters>
+            <customFilter operator="lessThan" val="0"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>3</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03DE998B-EA76-4ABF-92E3-8311DF83E2EA}" name="CustomRules" displayName="CustomRules" ref="A2:I30" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A2:I30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A14CF05F-33E8-4D5E-8165-2C6687D96614}" name="Priority"/>
+    <tableColumn id="2" xr3:uid="{C681B94A-B9C0-4261-8780-DD8F9142AF4F}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{A5C757D0-C1A7-464E-921B-8C7088523E3C}" name="Match Type"/>
+    <tableColumn id="4" xr3:uid="{61DBA4C5-B16A-42C9-AB5B-B76A7888391C}" name="Pattern"/>
+    <tableColumn id="5" xr3:uid="{5823C2B0-22E8-4EB4-84D4-DF7141C179DA}" name="Direction"/>
+    <tableColumn id="6" xr3:uid="{CBC38F70-518F-4956-B639-F3BD79362BCF}" name="Txn Type Contains"/>
+    <tableColumn id="7" xr3:uid="{1AEF6E40-5D22-48AC-8256-F6CC899880A5}" name="Active"/>
+    <tableColumn id="8" xr3:uid="{8179FEE3-9D69-4C57-A3EF-7D913158078E}" name="Notes"/>
+    <tableColumn id="10" xr3:uid="{5A8A66D8-9936-4C53-AE3B-288EF534BE02}" name="Global Category"/>
+  </tableColumns>
+  <tableStyleInfo name="None" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C49A2DF6-76BD-481F-B3EC-BDFE908FF5E0}" name="TransactionData" displayName="TransactionData" ref="A1:J2" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{FE34A13D-4148-4699-86C1-88057DF34BF6}" name="T/N"/>
+    <tableColumn id="2" xr3:uid="{58BD9C60-160E-4CF1-94B9-70076C3DFD04}" name="Date" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{87D2A9BE-8F22-4574-A6F0-96282D84D911}" name="Transaction Type"/>
+    <tableColumn id="4" xr3:uid="{58D5972E-C899-4502-97F4-D46A140CB239}" name="Description"/>
+    <tableColumn id="5" xr3:uid="{67D17DC2-3EA0-4A94-B70E-E8C451FBD6EE}" name="Amount" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{B282A55C-1A49-406B-9048-94404E26D862}" name="Balance" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{1A53D46A-3811-42CF-9D6F-35DCAD1589B0}" name="Global"/>
+    <tableColumn id="8" xr3:uid="{111DB7A8-E069-44CE-830D-848E85A4CA1A}" name="Custom"/>
+    <tableColumn id="9" xr3:uid="{0C2EC26A-B2A5-4E39-8E44-9DA45638CA67}" name="Manual"/>
+    <tableColumn id="10" xr3:uid="{672E2CEC-2331-497B-8F0D-3312D783F974}" name="Final"/>
+  </tableColumns>
+  <tableStyleInfo name="None" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -578,13 +1156,738 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C426494E-1CA8-4709-9C46-91FDF51619D3}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811F575A-AA26-4648-AB3C-E6729FC9A6D6}">
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="9.140625" style="6"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="12.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="5" t="e" cm="1" vm="1">
+        <f t="array" ref="G1">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(TransactionData[Final],TransactionData[Final]&lt;&gt;"")))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H1" s="7" cm="1">
+        <f t="array" ref="H1">_xlfn.LET(_xlpm.cats,_xlfn.ANCHORARRAY(G1),_xlfn.MAP(_xlpm.cats,_xlfn.LAMBDA(_xlpm.c,SUMIF(TransactionData[Final],_xlpm.c,TransactionData[Amount]))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F8D5F6-CEEA-4D69-BBAD-120B0BA43CBB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" errorTitle="Invalid Priority" error="Priority must be a whole number." promptTitle="Priority" prompt="Enter a whole number." sqref="A6:A4992 A1 A3:A4" xr:uid="{7B417E1D-CB4B-41F1-A2AB-26AE1D7337FD}"/>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LMr Reiss Cartwright&amp;CCustom Rules&amp;R01/01/25 - 31/12/25</oddHeader>
+    <evenHeader>&amp;LMr Reiss Cartwright&amp;CCustom Rules&amp;R01/01/25 - 31/12/25</evenHeader>
+    <firstHeader>&amp;LMr Reiss Cartwright&amp;CCustom Rules&amp;R01/01/25 - 31/12/25</firstHeader>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D125E940-BC16-411A-8551-4A0654E38DD6}">
+          <x14:formula1>
+            <xm:f>Helper!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{49B6C10E-B33F-4274-9C5D-10CC6AE0A855}">
+          <x14:formula1>
+            <xm:f>Helper!$C:$C</xm:f>
+          </x14:formula1>
+          <xm:sqref>G3:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6005C364-B22A-4FF2-825B-2B1B017EEACB}">
+          <x14:formula1>
+            <xm:f>Helper!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C46041D-B82C-4398-9676-2482F5A09153}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="4" width="20" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="10" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;LMr Reiss Cartwright&amp;CTransaction Data&amp;R01/01/25 - 31/12/25</oddHeader>
+    <evenHeader>&amp;LMr Reiss Cartwright&amp;CTransaction Data&amp;R01/01/25 - 31/12/25</evenHeader>
+    <firstHeader>&amp;LMr Reiss Cartwright&amp;CTransaction Data&amp;R01/01/25 - 31/12/25</firstHeader>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2A1513-7C05-46BE-B5B9-6DC2793D874C}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
+    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="4">
+        <f>IFERROR(SUM(_xlfn.ANCHORARRAY(B3)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IFERROR(SUM(_xlfn.ANCHORARRAY(E3)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="str" cm="1">
+        <f t="array" ref="A3">_xlfn.LET(_xlpm.cats,_xlfn.ANCHORARRAY([1]Helper!G1),_xlpm.tots,_xlfn.ANCHORARRAY([1]Helper!H1),IFERROR(_xlfn._xlws.FILTER(_xlpm.cats,_xlpm.tots&gt;0),""))</f>
+        <v/>
+      </c>
+      <c r="B3" s="4" t="str" cm="1">
+        <f t="array" ref="B3">_xlfn.LET(_xlpm.tots,_xlfn.ANCHORARRAY([1]Helper!H1),IFERROR(_xlfn._xlws.FILTER(_xlpm.tots,_xlpm.tots&gt;0),""))</f>
+        <v/>
+      </c>
+      <c r="D3" s="1" t="str" cm="1">
+        <f t="array" ref="D3">_xlfn.LET(_xlpm.cats,_xlfn.ANCHORARRAY([1]Helper!G1),_xlpm.tots,_xlfn.ANCHORARRAY([1]Helper!H1),IFERROR(_xlfn._xlws.FILTER(_xlpm.cats,_xlpm.tots&lt;0),""))</f>
+        <v/>
+      </c>
+      <c r="E3" s="4" t="str" cm="1">
+        <f t="array" ref="E3">_xlfn.LET(_xlpm.tots,_xlfn.ANCHORARRAY([1]Helper!H1),IFERROR(-_xlfn._xlws.FILTER(_xlpm.tots,_xlpm.tots&lt;0),""))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</oddHeader>
+    <evenHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</evenHeader>
+    <firstHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EF9C52-966D-4A69-A8FE-26E0C81CA230}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1"/>
+      <c r="D1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2"/>
+      <c r="D2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</oddHeader>
+    <evenHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</evenHeader>
+    <firstHeader>&amp;LMr Reiss Cartwright&amp;CSummary&amp;R01/01/25 - 31/12/25</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007DDDC61C6EBC344ABFB35175DB918FFD" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf49863f079209c9ede733a84f37b3f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4708ced-508a-40d3-8001-943584fcd60d" xmlns:ns3="27721ca5-1d6b-4993-be98-25087674e91f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9805f82215c861d592a476dcd5b251a7" ns2:_="" ns3:_="">
+    <xsd:import namespace="e4708ced-508a-40d3-8001-943584fcd60d"/>
+    <xsd:import namespace="27721ca5-1d6b-4993-be98-25087674e91f"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e4708ced-508a-40d3-8001-943584fcd60d" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0de65450-8985-4c50-92d9-b5776b2607d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="27721ca5-1d6b-4993-be98-25087674e91f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{29a6217b-98ce-428b-9da1-106c7a3eafea}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="27721ca5-1d6b-4993-be98-25087674e91f">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="27721ca5-1d6b-4993-be98-25087674e91f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4708ced-508a-40d3-8001-943584fcd60d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6217D5DB-5826-43BF-BDB4-5B0FC8577121}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e4708ced-508a-40d3-8001-943584fcd60d"/>
+    <ds:schemaRef ds:uri="27721ca5-1d6b-4993-be98-25087674e91f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F431B751-EB44-4B30-A779-C62701F8D681}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="27721ca5-1d6b-4993-be98-25087674e91f"/>
+    <ds:schemaRef ds:uri="e4708ced-508a-40d3-8001-943584fcd60d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8273B8-C170-44D6-B7F5-B02A7B74441C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ExcelTemplate.xlsx
+++ b/ExcelTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://parkersaccountancy.sharepoint.com/sites/ParkersAccountancy/Shared Documents/George/PDF-Converter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="8_{DE894061-B1CA-4F02-BBC5-E3F190B4CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C629BEAA-1B7B-4AD6-A51B-CCF5C8EC98B9}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="8_{DE894061-B1CA-4F02-BBC5-E3F190B4CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27661846-43C8-49FB-9702-478BF164A1A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3F22E0B9-65B0-45DD-B4C4-92AA6084518F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3F22E0B9-65B0-45DD-B4C4-92AA6084518F}"/>
   </bookViews>
   <sheets>
     <sheet name="Helper" sheetId="5" state="hidden" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId7"/>
+    <pivotCache cacheId="19" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -185,9 +185,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-\£* #,##0.00_-;[Red]\£* #,##0.00_-;_-\£* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -267,7 +268,7 @@
     <xf numFmtId="44" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
@@ -286,10 +287,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -313,6 +316,21 @@
       <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="34" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -330,21 +348,6 @@
       <font>
         <b/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -551,7 +554,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="George Farrell" refreshedDate="46086.704445949072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{E30527A9-8550-465B-90F3-1350603B8E86}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="George Farrell" refreshedDate="46086.708017476849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{E30527A9-8550-465B-90F3-1350603B8E86}">
   <cacheSource type="worksheet">
     <worksheetSource name="TransactionData"/>
   </cacheSource>
@@ -615,7 +618,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86028C4-318E-4098-AF19-D8817826B302}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Income">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E86028C4-318E-4098-AF19-D8817826B302}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Income">
   <location ref="A1:B2" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -672,7 +675,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C87894D-13D6-46EA-81BF-345BEBF15C8B}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expenses">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C87894D-13D6-46EA-81BF-345BEBF15C8B}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expenses">
   <location ref="D1:E2" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -706,19 +709,19 @@
     <dataField name="Amount " fld="4" baseField="9" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="14">
+    <format dxfId="9">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="7">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -804,7 +807,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03DE998B-EA76-4ABF-92E3-8311DF83E2EA}" name="CustomRules" displayName="CustomRules" ref="A2:I30" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03DE998B-EA76-4ABF-92E3-8311DF83E2EA}" name="CustomRules" displayName="CustomRules" ref="A2:I30" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A2:I30" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A14CF05F-33E8-4D5E-8165-2C6687D96614}" name="Priority"/>
@@ -822,15 +825,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C49A2DF6-76BD-481F-B3EC-BDFE908FF5E0}" name="TransactionData" displayName="TransactionData" ref="A1:J2" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C49A2DF6-76BD-481F-B3EC-BDFE908FF5E0}" name="TransactionData" displayName="TransactionData" ref="A1:J2" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FE34A13D-4148-4699-86C1-88057DF34BF6}" name="T/N"/>
-    <tableColumn id="2" xr3:uid="{58BD9C60-160E-4CF1-94B9-70076C3DFD04}" name="Date" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{58BD9C60-160E-4CF1-94B9-70076C3DFD04}" name="Date" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{87D2A9BE-8F22-4574-A6F0-96282D84D911}" name="Transaction Type"/>
     <tableColumn id="4" xr3:uid="{58D5972E-C899-4502-97F4-D46A140CB239}" name="Description"/>
-    <tableColumn id="5" xr3:uid="{67D17DC2-3EA0-4A94-B70E-E8C451FBD6EE}" name="Amount" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{B282A55C-1A49-406B-9048-94404E26D862}" name="Balance" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{67D17DC2-3EA0-4A94-B70E-E8C451FBD6EE}" name="Amount" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{B282A55C-1A49-406B-9048-94404E26D862}" name="Balance" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{1A53D46A-3811-42CF-9D6F-35DCAD1589B0}" name="Global"/>
     <tableColumn id="8" xr3:uid="{111DB7A8-E069-44CE-830D-848E85A4CA1A}" name="Custom"/>
     <tableColumn id="9" xr3:uid="{0C2EC26A-B2A5-4E39-8E44-9DA45638CA67}" name="Manual"/>
@@ -1236,17 +1239,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1406,13 +1409,13 @@
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1424,10 +1427,10 @@
         <f>IFERROR(SUM(_xlfn.ANCHORARRAY(B3)),0)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="17">
         <f>IFERROR(SUM(_xlfn.ANCHORARRAY(E3)),0)</f>
         <v>0</v>
       </c>
@@ -1634,6 +1637,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="27721ca5-1d6b-4993-be98-25087674e91f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4708ced-508a-40d3-8001-943584fcd60d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007DDDC61C6EBC344ABFB35175DB918FFD" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf49863f079209c9ede733a84f37b3f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4708ced-508a-40d3-8001-943584fcd60d" xmlns:ns3="27721ca5-1d6b-4993-be98-25087674e91f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9805f82215c861d592a476dcd5b251a7" ns2:_="" ns3:_="">
     <xsd:import namespace="e4708ced-508a-40d3-8001-943584fcd60d"/>
@@ -1834,27 +1857,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="27721ca5-1d6b-4993-be98-25087674e91f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4708ced-508a-40d3-8001-943584fcd60d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F431B751-EB44-4B30-A779-C62701F8D681}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="27721ca5-1d6b-4993-be98-25087674e91f"/>
+    <ds:schemaRef ds:uri="e4708ced-508a-40d3-8001-943584fcd60d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8273B8-C170-44D6-B7F5-B02A7B74441C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6217D5DB-5826-43BF-BDB4-5B0FC8577121}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1871,23 +1893,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F431B751-EB44-4B30-A779-C62701F8D681}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="27721ca5-1d6b-4993-be98-25087674e91f"/>
-    <ds:schemaRef ds:uri="e4708ced-508a-40d3-8001-943584fcd60d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8273B8-C170-44D6-B7F5-B02A7B74441C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>